--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入出金・売上" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="入出金・売上" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <color rgb="00888888"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -70,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -82,6 +89,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,15 +460,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -531,6 +544,104 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>出金 1件</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0810918384(001)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>三井住友銀行（トランクNORTH支店 普通）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>出金 1件（振込／依頼人 デンシシ-ビ-ノウホウ）※金額メール未記載・Web21明細で要確認</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>通知番号20260810-10016887</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>（集計）</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>入金計</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>出金計</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>※三井住友の1件は金額未記載のため出金計に含まず</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="入出金・売上" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入出金・売上" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -613,30 +613,65 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>（集計）</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>入金計</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>0</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>出金 1件</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0812926926(001)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12 転送受信</t>
+        </is>
       </c>
     </row>
     <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>（集計）</t>
+        </is>
+      </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
+          <t>入金計</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="C7" s="7" t="n">
+        <v>430000</v>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>※三井住友の1件は金額未記載のため出金計に含まず</t>
         </is>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>出金 1件</t>
+          <t>出金 1件（山中 役員報酬）</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,15 +460,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -648,32 +648,65 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>（集計）</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>入金計</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>0</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>三井住友銀行（トランクNORTH支店 普通）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>出金 1件（振込／土壌検査代）※金額メール未記載・Web21明細で要確認</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>依頼人 デンシシ-ビ-ノウホウ</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-18 転送受信</t>
+        </is>
       </c>
     </row>
     <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>（集計）</t>
+        </is>
+      </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
+          <t>入金計</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C8" s="7" t="n">
         <v>430000</v>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>※三井住友の1件は金額未記載のため出金計に含まず</t>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>※三井住友の2件は金額未記載のため出金計に含まず</t>
         </is>
       </c>
     </row>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,14 +460,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
@@ -681,32 +681,70 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>三井住友銀行（トランクNORTH支店 普通）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>振込入金 1件 ※金額・振込元メール未記載・Web21「振込入金明細照会」で要確認</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>通知番号20260819-10050020</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C8" s="7" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>※三井住友の入金1件は金額未記載のため未算入</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C9" s="7" t="n">
         <v>430000</v>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>※三井住友の2件は金額未記載のため出金計に含まず</t>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>※三井住友の出金2件は金額未記載のため未算入</t>
         </is>
       </c>
     </row>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -714,37 +714,70 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>三井住友銀行（トランクNORTH支店 普通）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>出金 1件 ※金額・内容メール未記載・Web21「入出金明細照会」で要確認</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>通知番号20260821-10101365</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>※三井住友の入金1件は金額未記載のため未算入</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="6" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C10" s="7" t="n">
         <v>430000</v>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>※三井住友の出金2件は金額未記載のため未算入</t>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>※三井住友の出金3件は金額未記載のため未算入</t>
         </is>
       </c>
     </row>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -747,35 +747,70 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>出金 1件</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0824964860(001)</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>※三井住友の入金1件は金額未記載のため未算入</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="6" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
-        <v>430000</v>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C11" s="7" t="n">
+        <v>440000</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>※三井住友の出金3件は金額未記載のため未算入</t>
         </is>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,14 +460,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
@@ -782,35 +782,173 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>369050</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>入金 1件</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0825975230(001)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>30140</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>入金 1件</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0825975561(001)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>三井住友銀行（トランクNORTH支店 普通）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>振込入金 1件 ※金額・振込元メール未記載・Web21「振込入金明細照会」で要確認</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>通知番号20260825-10039731</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>9400</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Square（カード決済）</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>売上：鈴木久貴様 カード決済／総売上¥8,546＋消費税¥854＝¥9,400・決済手数料¥338・純受取¥9,062（銀行入金は後日）</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Square日次売上サマリー</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25 受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>※三井住友の入金1件は金額未記載のため未算入</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+      <c r="C14" s="7" t="n">
+        <v>408590</v>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>※三井住友の入金2件は金額未記載のため未算入。Squareは税込売上（銀行入金は後日・純¥9,062）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C15" s="7" t="n">
         <v>440000</v>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>※三井住友の出金3件は金額未記載のため未算入</t>
         </is>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,14 +460,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
@@ -905,7 +905,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>売上：鈴木久貴様 カード決済／総売上¥8,546＋消費税¥854＝¥9,400・決済手数料¥338・純受取¥9,062（銀行入金は後日）</t>
+          <t>売上：鈴木久貴様 カード決済／総売上¥8,546＋消費税¥854＝¥9,400・決済手数料¥338・純受取¥9,062（8/27 銀行入金済＝下記メモ、重複計上せず）</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -920,35 +920,70 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>38800</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>出金 2件</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0827987987(001)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C15" s="7" t="n">
         <v>408590</v>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>※三井住友の入金2件は金額未記載のため未算入。Squareは税込売上（銀行入金は後日・純¥9,062）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="6" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>※三井住友の入金2件は金額未記載のため未算入。Squareは税込売上¥9,400で計上（銀行実入金¥9,062は重複計上せず）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
-        <v>440000</v>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="C16" s="7" t="n">
+        <v>478800</v>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>※三井住友の出金3件は金額未記載のため未算入</t>
         </is>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>売上：鈴木久貴様 カード決済／総売上¥8,546＋消費税¥854＝¥9,400・決済手数料¥338・純受取¥9,062（8/27 銀行入金済＝下記メモ、重複計上せず）</t>
+          <t>売上：鈴木久貴様 カード決済／総売上¥8,546＋消費税¥854＝¥9,400・決済手数料¥338・純受取¥9,062（8/28 京信着金＝下記行）</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -955,35 +955,70 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>9062</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>入金 1件 《着金・売上計上済》 Square純受取¥9,062の着金（8/25 ¥9,400売上の実入金のため入金計に重複計上せず）</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0828997754(001)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C16" s="7" t="n">
         <v>408590</v>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>※三井住友の入金2件は金額未記載のため未算入。Squareは税込売上¥9,400で計上（銀行実入金¥9,062は重複計上せず）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="6" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>※三井住友の入金2件は金額未記載のため未算入。Square売上¥9,400で計上済み。8/28京信着金¥9,062は同売上の実入金のため重複算入せず</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C17" s="7" t="n">
         <v>478800</v>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>※三井住友の出金3件は金額未記載のため未算入</t>
         </is>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -990,35 +990,105 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>出金 1件</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0831003955(001)</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>10380</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>出金 2件</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0831010791(001)</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C18" s="7" t="n">
         <v>408590</v>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>※三井住友の入金2件は金額未記載のため未算入。Square売上¥9,400で計上済み。8/28京信着金¥9,062は同売上の実入金のため重複算入せず</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
-        <v>478800</v>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="C19" s="7" t="n">
+        <v>539180</v>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>※三井住友の出金3件は金額未記載のため未算入</t>
         </is>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1060,35 +1060,171 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>三井住友銀行（トランクNORTH支店 普通）</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>振込入金 1件 ※金額メール未記載・Web21「振込入金明細照会」で要確認</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Web21通知（8/31 23:47）</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>三井住友銀行（トランクNORTH支店 普通）</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>振込 1件（振込メモ：小口現金／承認者 山中俊成）※金額メール未記載・残高差引では約10,145円・Web21明細で要確認</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Web21振込受付完了（9/1）</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>出金 1件（BB手数料の可能性）</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0901019150(001)</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>15350</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>入金 1件</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0901024739(001)</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
-        <v>408590</v>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="C22" s="7" t="n">
+        <v>423940</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>※三井住友の入金2件は金額未記載のため未算入。Square売上¥9,400で計上済み。8/28京信着金¥9,062は同売上の実入金のため重複算入せず</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="6" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n">
-        <v>539180</v>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="C23" s="7" t="n">
+        <v>540280</v>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>※三井住友の出金3件は金額未記載のため未算入</t>
         </is>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1196,35 +1196,140 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>40110</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>出金 2件</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0902030779(001)</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>84200</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>入金 1件</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0902031918(001)</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>8291</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>出金 2件</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>連絡番号0902032262(001)</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
-        <v>423940</v>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="C25" s="7" t="n">
+        <v>508140</v>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>※三井住友の入金2件は金額未記載のため未算入。Square売上¥9,400で計上済み。8/28京信着金¥9,062は同売上の実入金のため重複算入せず</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="6" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n">
-        <v>540280</v>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="C26" s="7" t="n">
+        <v>588681</v>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>※三井住友の出金3件は金額未記載のため未算入</t>
         </is>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1301,37 +1301,77 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>30110</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>出金 2件</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>連絡番号0907054040(001)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-09-07 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C26" s="7" t="n">
         <v>508140</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>※三井住友の入金2件は金額未記載のため未算入。Square売上¥9,400で計上済み。8/28京信着金¥9,062は同売上の実入金のため重複算入せず</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>588681</v>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="C27" s="7" t="n">
+        <v>618791</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>※三井住友の出金3件は金額未記載のため未算入</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>※三井住友の出金3件は金額未記載のため未算入。9/7京信 出金30,110円を追加</t>
         </is>
       </c>
     </row>
